--- a/product_selector_out/STM8 8-bit MCUs.xlsx
+++ b/product_selector_out/STM8 8-bit MCUs.xlsx
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AG43" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="AG44" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="AG45" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="AG46" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -21591,7 +21591,7 @@
       </c>
       <c r="AG135" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="AG136" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="AG137" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AG138" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="AG139" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22426,7 +22426,7 @@
       </c>
       <c r="AG140" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22927,7 +22927,7 @@
       </c>
       <c r="AG143" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -23094,7 +23094,7 @@
       </c>
       <c r="AG144" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -23261,7 +23261,7 @@
       </c>
       <c r="AG145" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -29099,19 +29099,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="X43" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z43" s="6" t="inlineStr">
@@ -29149,9 +29149,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG43" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -29266,19 +29266,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="X44" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z44" s="6" t="inlineStr">
@@ -29316,9 +29316,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG44" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -29433,19 +29433,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W45" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="X45" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y45" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z45" s="6" t="inlineStr">
@@ -29483,9 +29483,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG45" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -29600,19 +29600,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="X46" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y46" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z46" s="6" t="inlineStr">
@@ -29650,9 +29650,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG46" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44473,9 +44473,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y135" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y135" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z135" s="6" t="inlineStr">
@@ -44513,9 +44513,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG135" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG135" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44640,9 +44640,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y136" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y136" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z136" s="6" t="inlineStr">
@@ -44680,9 +44680,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG136" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG136" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44807,9 +44807,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y137" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y137" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z137" s="6" t="inlineStr">
@@ -44847,9 +44847,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG137" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG137" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44974,9 +44974,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y138" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y138" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z138" s="6" t="inlineStr">
@@ -45014,9 +45014,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG138" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG138" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -45141,9 +45141,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y139" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y139" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z139" s="6" t="inlineStr">
@@ -45181,9 +45181,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG139" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG139" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -45308,9 +45308,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y140" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y140" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z140" s="6" t="inlineStr">
@@ -45348,9 +45348,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG140" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG140" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -45799,24 +45799,24 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W143" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="X143" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y143" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="Z143" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W143" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X143" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y143" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Z143" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AA143" s="7" t="inlineStr">
@@ -45849,9 +45849,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG143" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG143" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -45966,24 +45966,24 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W144" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="X144" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y144" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="Z144" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W144" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X144" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y144" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Z144" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AA144" s="7" t="inlineStr">
@@ -46016,9 +46016,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG144" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG144" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -46133,24 +46133,24 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W145" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="X145" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y145" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="Z145" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W145" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X145" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y145" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Z145" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AA145" s="7" t="inlineStr">
@@ -46183,9 +46183,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG145" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG145" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -46204,7 +46204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -46429,7 +46429,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -46473,7 +46473,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -46517,7 +46517,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -46561,7 +46561,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -46605,7 +46605,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -46649,7 +46649,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -46678,12 +46678,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM8AL3L46</t>
+          <t>STM8L001J3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -46693,14 +46693,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM8AL3L46</t>
+          <t>STM8L050J3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -46715,19 +46715,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 25. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM8AL3L48</t>
+          <t>STM8L051F3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -46737,14 +46737,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM8AL3L48</t>
+          <t>STM8L052R8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -46759,19 +46759,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 17. Total current consumption in Run mode; Table 25. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM8AL3L66</t>
+          <t>STM8L052R8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -46781,14 +46781,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. Total current consumption in Run mode</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM8AL3L66</t>
+          <t>STM8L101F1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -46803,19 +46803,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM8AL3L68</t>
+          <t>STM8L101F2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -46825,14 +46825,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM8AL3L68</t>
+          <t>STM8L101F3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -46847,14 +46847,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM8L001J3</t>
+          <t>STM8L101G2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -46869,14 +46869,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 19. Peripheral current consumption</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM8L050J3</t>
+          <t>STM8L101G3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -46891,14 +46891,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption under external reset</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM8L051F3</t>
+          <t>STM8L101K3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -46913,14 +46913,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption under external reset</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM8L052R8</t>
+          <t>STM8L151C2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -46935,19 +46935,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 17. Total current consumption in Run mode; Table 25. Current consumption under external reset</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM8L052R8</t>
+          <t>STM8L151C3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -46957,14 +46957,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 17. Total current consumption in Run mode</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM8L101F1</t>
+          <t>STM8L151C4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -46979,14 +46979,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 28. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM8L101F2</t>
+          <t>STM8L151C6</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -47001,14 +47001,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM8L101F3</t>
+          <t>STM8L151C8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -47023,14 +47023,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM8L101G2</t>
+          <t>STM8L151F2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -47045,14 +47045,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM8L101G3</t>
+          <t>STM8L151F3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -47067,14 +47067,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM8L101K3</t>
+          <t>STM8L151G2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -47089,14 +47089,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM8L151C2</t>
+          <t>STM8L151G3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -47118,7 +47118,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM8L151C3</t>
+          <t>STM8L151G4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -47140,7 +47140,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM8L151C4</t>
+          <t>STM8L151G6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -47155,14 +47155,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 28. Current consumption under external reset</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM8L151C6</t>
+          <t>STM8L151K2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -47184,7 +47184,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM8L151C8</t>
+          <t>STM8L151K3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -47206,7 +47206,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM8L151F2</t>
+          <t>STM8L151K4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -47228,7 +47228,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM8L151F3</t>
+          <t>STM8L151K6</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -47250,7 +47250,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM8L151G2</t>
+          <t>STM8L151M8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -47272,7 +47272,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM8L151G3</t>
+          <t>STM8L151R6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -47287,19 +47287,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 20. Total current consumption in Run mode; Table 28. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM8L151G4</t>
+          <t>STM8L151R6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -47309,14 +47309,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 20. Total current consumption in Run mode</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM8L151G6</t>
+          <t>STM8L151R8</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -47338,7 +47338,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM8L151K2</t>
+          <t>STM8L152C4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -47360,7 +47360,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM8L151K3</t>
+          <t>STM8L152C6</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -47382,7 +47382,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM8L151K4</t>
+          <t>STM8L152C8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -47404,7 +47404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM8L151K6</t>
+          <t>STM8L152K4</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -47426,7 +47426,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM8L151M8</t>
+          <t>STM8L152K6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -47448,7 +47448,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM8L151R6</t>
+          <t>STM8L152K8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -47463,19 +47463,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption in Run mode; Table 28. Current consumption under external reset</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM8L151R6</t>
+          <t>STM8L152M8</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -47485,14 +47485,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption in Run mode</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM8L151R8</t>
+          <t>STM8L152R6</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -47514,7 +47514,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM8L152C4</t>
+          <t>STM8L152R8</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -47536,7 +47536,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM8L152C6</t>
+          <t>STM8L162M8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -47551,19 +47551,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 19. Total current consumption in Run mode; Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM8L152C8</t>
+          <t>STM8L162M8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -47573,14 +47573,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 19. Total current consumption in Run mode</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM8L152K4</t>
+          <t>STM8L162R8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -47595,19 +47595,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 19. Total current consumption in Run mode; Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM8L152K6</t>
+          <t>STM8L162R8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -47617,14 +47617,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 19. Total current consumption in Run mode</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM8L152K8</t>
+          <t>STM8S001J3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -47639,14 +47639,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM8L152M8</t>
+          <t>STM8S003F3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -47661,14 +47661,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 30. Total current consumption and timing in forced reset state; Table 31. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM8L152R6</t>
+          <t>STM8S003K3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -47683,14 +47683,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM8L152R8</t>
+          <t>STM8S005C6</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -47705,14 +47705,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM8L162M8</t>
+          <t>STM8S005K6</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -47727,19 +47727,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 19. Total current consumption in Run mode; Table 27. Current consumption under external reset</t>
+          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM8L162M8</t>
+          <t>STM8S007C8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -47749,14 +47749,14 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 19. Total current consumption in Run mode</t>
+          <t>Table 27. Total current consumption and timing in forced reset state; Table 28. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM8L162R8</t>
+          <t>STM8S103F2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -47771,19 +47771,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 19. Total current consumption in Run mode; Table 27. Current consumption under external reset</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM8L162R8</t>
+          <t>STM8S103F3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -47793,14 +47793,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 19. Total current consumption in Run mode</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM8S001J3</t>
+          <t>STM8S103K3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -47815,14 +47815,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM8S003F3</t>
+          <t>STM8S105C4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -47837,14 +47837,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 30. Total current consumption and timing in forced reset state; Table 31. Peripheral current consumption</t>
+          <t>Table 29. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM8S003K3</t>
+          <t>STM8S105C6</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -47859,14 +47859,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM8S005C6</t>
+          <t>STM8S105K4</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -47881,14 +47881,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM8S005K6</t>
+          <t>STM8S105K6</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -47903,14 +47903,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM8S007C8</t>
+          <t>STM8S105S4</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -47925,14 +47925,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 27. Total current consumption and timing in forced reset state; Table 28. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM8S103F2</t>
+          <t>STM8S105S6</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -47954,7 +47954,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM8S103F3</t>
+          <t>STM8S207C6</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -47969,14 +47969,14 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM8S103K3</t>
+          <t>STM8S207C8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -47991,14 +47991,14 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM8S105C4</t>
+          <t>STM8S207CB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -48013,14 +48013,14 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 29. Total current consumption and timing in forced reset state</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM8S105C6</t>
+          <t>STM8S207K6</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -48035,14 +48035,14 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM8S105K4</t>
+          <t>STM8S207K8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -48057,14 +48057,14 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM8S105K6</t>
+          <t>STM8S207M8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -48079,14 +48079,14 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM8S105S4</t>
+          <t>STM8S207MB</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -48101,14 +48101,14 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM8S105S6</t>
+          <t>STM8S207R6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -48123,14 +48123,14 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM8S207C6</t>
+          <t>STM8S207R8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -48152,7 +48152,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM8S207C8</t>
+          <t>STM8S207RB</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -48174,7 +48174,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM8S207CB</t>
+          <t>STM8S207S6</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -48196,7 +48196,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM8S207K6</t>
+          <t>STM8S207S8</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -48218,7 +48218,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM8S207K8</t>
+          <t>STM8S207SB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -48240,7 +48240,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM8S207M8</t>
+          <t>STM8S208C6</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -48262,7 +48262,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM8S207MB</t>
+          <t>STM8S208C8</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -48284,7 +48284,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM8S207R6</t>
+          <t>STM8S208CB</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -48306,7 +48306,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM8S207R8</t>
+          <t>STM8S208MB</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -48328,7 +48328,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM8S207RB</t>
+          <t>STM8S208R8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -48350,7 +48350,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM8S207S6</t>
+          <t>STM8S208RB</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -48372,7 +48372,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM8S207S8</t>
+          <t>STM8S208S6</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -48394,7 +48394,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM8S207SB</t>
+          <t>STM8S903F3</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -48409,14 +48409,14 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 23. Total current consumption with code execution in run mode at V = 5 V; Table 32. Total current consumption and timing in forced reset state; Table 33. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM8S208C6</t>
+          <t>STM8S903K3</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -48431,14 +48431,14 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 23. Total current consumption with code execution in run mode at V = 5 V; Table 32. Total current consumption and timing in forced reset state; Table 33. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM8S208C8</t>
+          <t>STM8SPLNB1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -48453,14 +48453,14 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 24. Total current consumption at V = 5 V</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM8S208CB</t>
+          <t>STM8AF628A</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -48475,14 +48475,14 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 29. Total current consumption with code execution in run mode at V = 5 V; Table 38. Total current consumption and timing in forced reset state; Table 39. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM8S208MB</t>
+          <t>STM8AF62AA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -48497,14 +48497,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 29. Total current consumption with code execution in run mode at V = 5 V; Table 38. Total current consumption and timing in forced reset state; Table 39. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM8S208R8</t>
+          <t>STM8AL3188</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -48519,14 +48519,14 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 29. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM8S208RB</t>
+          <t>STM8AL3189</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -48541,19 +48541,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 29. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM8S208S6</t>
+          <t>STM8AL318A</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -48563,14 +48563,14 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM8S903F3</t>
+          <t>STM8AL318A</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -48585,14 +48585,14 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 23. Total current consumption with code execution in run mode at V = 5 V; Table 32. Total current consumption and timing in forced reset state; Table 33. Peripheral current consumption</t>
+          <t>Table 29. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM8S903K3</t>
+          <t>STM8AL31E88</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -48607,19 +48607,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Table 23. Total current consumption with code execution in run mode at V = 5 V; Table 32. Total current consumption and timing in forced reset state; Table 33. Peripheral current consumption</t>
+          <t>Table 29. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM8SPLNB1</t>
+          <t>STM8AL31E89</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -48629,14 +48629,14 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 24. Total current consumption at V = 5 V</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM8AF628A</t>
+          <t>STM8AL31E89</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48651,19 +48651,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Table 29. Total current consumption with code execution in run mode at V = 5 V; Table 38. Total current consumption and timing in forced reset state; Table 39. Peripheral current consumption</t>
+          <t>Table 29. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM8AF62AA</t>
+          <t>STM8AL31E8A</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -48673,14 +48673,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 29. Total current consumption with code execution in run mode at V = 5 V; Table 38. Total current consumption and timing in forced reset state; Table 39. Peripheral current consumption</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM8AL3188</t>
+          <t>STM8AL31E8A</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -48702,7 +48702,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM8AL3189</t>
+          <t>STM8TL52F4</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -48717,19 +48717,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM8AL318A</t>
+          <t>STM8TL52F4</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -48739,14 +48739,14 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM8AL318A</t>
+          <t>STM8TL52G4</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -48761,19 +48761,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM8AL31E88</t>
+          <t>STM8TL52G4</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -48782,446 +48782,6 @@
         </is>
       </c>
       <c r="D117" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>STM8AL31E89</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>STM8AL31E89</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>STM8AL31E8A</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>STM8AL31E8A</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>STM8AL3L88</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>STM8AL3L89</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>STM8AL3L8A</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>STM8AL3LE88</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>STM8AL3LE89</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>STM8AL3LE8A</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>STM8TL52F4</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>STM8TL52F4</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>STM8TL52G4</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>STM8TL52G4</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>STM8TL53C4</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>STM8TL53C4</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>STM8TL53F4</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>STM8TL53F4</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>STM8TL53G4</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>STM8TL53G4</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
         <is>
           <t>Table 19. Total current consumption in Run mode (1)</t>
         </is>

--- a/product_selector_out/STM8 8-bit MCUs.xlsx
+++ b/product_selector_out/STM8 8-bit MCUs.xlsx
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AG43" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="AG44" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="AG45" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
     </row>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="AG46" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
     </row>
@@ -21591,7 +21591,7 @@
       </c>
       <c r="AG135" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
         </is>
       </c>
     </row>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="AG136" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
         </is>
       </c>
     </row>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="AG137" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
         </is>
       </c>
     </row>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AG138" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
         </is>
       </c>
     </row>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="AG139" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
         </is>
       </c>
     </row>
@@ -22426,7 +22426,7 @@
       </c>
       <c r="AG140" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
         </is>
       </c>
     </row>
@@ -22927,7 +22927,7 @@
       </c>
       <c r="AG143" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
         </is>
       </c>
     </row>
@@ -23094,7 +23094,7 @@
       </c>
       <c r="AG144" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
         </is>
       </c>
     </row>
@@ -23261,7 +23261,7 @@
       </c>
       <c r="AG145" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
         </is>
       </c>
     </row>
@@ -29099,19 +29099,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="X43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Y43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="W43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="X43" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="Y43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z43" s="6" t="inlineStr">
@@ -29149,9 +29149,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG43" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -29266,19 +29266,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="X44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Y44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="W44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="X44" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="Y44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z44" s="6" t="inlineStr">
@@ -29316,9 +29316,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG44" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -29433,19 +29433,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="X45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Y45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="W45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="X45" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="Y45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z45" s="6" t="inlineStr">
@@ -29483,9 +29483,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG45" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -29600,19 +29600,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="X46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Y46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="X46" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="Y46" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z46" s="6" t="inlineStr">
@@ -29650,9 +29650,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG46" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -44473,9 +44473,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y135" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="Y135" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z135" s="6" t="inlineStr">
@@ -44513,9 +44513,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG135" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG135" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -44640,9 +44640,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y136" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="Y136" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z136" s="6" t="inlineStr">
@@ -44680,9 +44680,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG136" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG136" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -44807,9 +44807,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y137" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="Y137" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z137" s="6" t="inlineStr">
@@ -44847,9 +44847,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG137" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG137" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -44974,9 +44974,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y138" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="Y138" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z138" s="6" t="inlineStr">
@@ -45014,9 +45014,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG138" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG138" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -45141,9 +45141,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y139" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="Y139" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z139" s="6" t="inlineStr">
@@ -45181,9 +45181,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG139" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG139" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -45308,9 +45308,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y140" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="Y140" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z140" s="6" t="inlineStr">
@@ -45348,9 +45348,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG140" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG140" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -45799,24 +45799,24 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W143" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="X143" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Y143" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Z143" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="W143" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="X143" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="Y143" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="Z143" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AA143" s="7" t="inlineStr">
@@ -45849,9 +45849,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG143" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG143" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -45966,24 +45966,24 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W144" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="X144" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Y144" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Z144" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="W144" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="X144" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="Y144" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="Z144" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AA144" s="7" t="inlineStr">
@@ -46016,9 +46016,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG144" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG144" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -46133,24 +46133,24 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W145" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="X145" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Y145" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Z145" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="W145" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="X145" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="Y145" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="Z145" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AA145" s="7" t="inlineStr">
@@ -46183,9 +46183,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG145" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG145" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -46204,7 +46204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -46678,12 +46678,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM8L001J3</t>
+          <t>STM8AL3L46</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -46693,14 +46693,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 19. Peripheral current consumption</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM8L050J3</t>
+          <t>STM8AL3L46</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -46715,19 +46715,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption under external reset</t>
+          <t>Table 29. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM8L051F3</t>
+          <t>STM8AL3L48</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -46737,14 +46737,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption under external reset</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM8L052R8</t>
+          <t>STM8AL3L48</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -46759,19 +46759,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 17. Total current consumption in Run mode; Table 25. Current consumption under external reset</t>
+          <t>Table 29. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM8L052R8</t>
+          <t>STM8AL3L66</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -46781,14 +46781,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 17. Total current consumption in Run mode</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM8L101F1</t>
+          <t>STM8AL3L66</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -46803,19 +46803,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 29. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM8L101F2</t>
+          <t>STM8AL3L68</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -46825,14 +46825,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM8L101F3</t>
+          <t>STM8AL3L68</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -46847,14 +46847,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 29. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM8L101G2</t>
+          <t>STM8L001J3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -46869,14 +46869,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 19. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM8L101G3</t>
+          <t>STM8L050J3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -46891,14 +46891,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 25. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM8L101K3</t>
+          <t>STM8L051F3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -46913,14 +46913,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 25. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM8L151C2</t>
+          <t>STM8L052R8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -46935,19 +46935,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 17. Total current consumption in Run mode; Table 25. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM8L151C3</t>
+          <t>STM8L052R8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -46957,14 +46957,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 17. Total current consumption in Run mode</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM8L151C4</t>
+          <t>STM8L101F1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -46979,14 +46979,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 28. Current consumption under external reset</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM8L151C6</t>
+          <t>STM8L101F2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -47001,14 +47001,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM8L151C8</t>
+          <t>STM8L101F3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -47023,14 +47023,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM8L151F2</t>
+          <t>STM8L101G2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -47045,14 +47045,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM8L151F3</t>
+          <t>STM8L101G3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -47067,14 +47067,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM8L151G2</t>
+          <t>STM8L101K3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -47089,14 +47089,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM8L151G3</t>
+          <t>STM8L151C2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -47118,7 +47118,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM8L151G4</t>
+          <t>STM8L151C3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -47140,7 +47140,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM8L151G6</t>
+          <t>STM8L151C4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -47155,14 +47155,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 28. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM8L151K2</t>
+          <t>STM8L151C6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -47184,7 +47184,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM8L151K3</t>
+          <t>STM8L151C8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -47206,7 +47206,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM8L151K4</t>
+          <t>STM8L151F2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -47228,7 +47228,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM8L151K6</t>
+          <t>STM8L151F3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -47250,7 +47250,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM8L151M8</t>
+          <t>STM8L151G2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -47272,7 +47272,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM8L151R6</t>
+          <t>STM8L151G3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -47287,19 +47287,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption in Run mode; Table 28. Current consumption under external reset</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM8L151R6</t>
+          <t>STM8L151G4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -47309,14 +47309,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption in Run mode</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM8L151R8</t>
+          <t>STM8L151G6</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -47338,7 +47338,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM8L152C4</t>
+          <t>STM8L151K2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -47360,7 +47360,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM8L152C6</t>
+          <t>STM8L151K3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -47382,7 +47382,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM8L152C8</t>
+          <t>STM8L151K4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -47404,7 +47404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM8L152K4</t>
+          <t>STM8L151K6</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -47426,7 +47426,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM8L152K6</t>
+          <t>STM8L151M8</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -47448,7 +47448,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM8L152K8</t>
+          <t>STM8L151R6</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -47463,19 +47463,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 20. Total current consumption in Run mode; Table 28. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM8L152M8</t>
+          <t>STM8L151R6</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -47485,14 +47485,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 20. Total current consumption in Run mode</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM8L152R6</t>
+          <t>STM8L151R8</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -47514,7 +47514,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM8L152R8</t>
+          <t>STM8L152C4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -47536,7 +47536,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM8L162M8</t>
+          <t>STM8L152C6</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -47551,19 +47551,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 19. Total current consumption in Run mode; Table 27. Current consumption under external reset</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM8L162M8</t>
+          <t>STM8L152C8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -47573,14 +47573,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 19. Total current consumption in Run mode</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM8L162R8</t>
+          <t>STM8L152K4</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -47595,19 +47595,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 19. Total current consumption in Run mode; Table 27. Current consumption under external reset</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM8L162R8</t>
+          <t>STM8L152K6</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -47617,14 +47617,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 19. Total current consumption in Run mode</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM8S001J3</t>
+          <t>STM8L152K8</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -47639,14 +47639,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM8S003F3</t>
+          <t>STM8L152M8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -47661,14 +47661,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 30. Total current consumption and timing in forced reset state; Table 31. Peripheral current consumption</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM8S003K3</t>
+          <t>STM8L152R6</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -47683,14 +47683,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM8S005C6</t>
+          <t>STM8L152R8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -47705,14 +47705,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM8S005K6</t>
+          <t>STM8L162M8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -47727,19 +47727,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
+          <t>Table 19. Total current consumption in Run mode; Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM8S007C8</t>
+          <t>STM8L162M8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -47749,14 +47749,14 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 27. Total current consumption and timing in forced reset state; Table 28. Peripheral current consumption</t>
+          <t>Table 19. Total current consumption in Run mode</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM8S103F2</t>
+          <t>STM8L162R8</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -47771,19 +47771,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 19. Total current consumption in Run mode; Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM8S103F3</t>
+          <t>STM8L162R8</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -47793,14 +47793,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 19. Total current consumption in Run mode</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM8S103K3</t>
+          <t>STM8S001J3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -47815,14 +47815,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM8S105C4</t>
+          <t>STM8S003F3</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -47837,14 +47837,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 29. Total current consumption and timing in forced reset state</t>
+          <t>Table 30. Total current consumption and timing in forced reset state; Table 31. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM8S105C6</t>
+          <t>STM8S003K3</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -47859,14 +47859,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM8S105K4</t>
+          <t>STM8S005C6</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -47881,14 +47881,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM8S105K6</t>
+          <t>STM8S005K6</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -47903,14 +47903,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM8S105S4</t>
+          <t>STM8S007C8</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -47925,14 +47925,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 27. Total current consumption and timing in forced reset state; Table 28. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM8S105S6</t>
+          <t>STM8S103F2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -47954,7 +47954,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM8S207C6</t>
+          <t>STM8S103F3</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -47969,14 +47969,14 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM8S207C8</t>
+          <t>STM8S103K3</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -47991,14 +47991,14 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM8S207CB</t>
+          <t>STM8S105C4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -48013,14 +48013,14 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 29. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM8S207K6</t>
+          <t>STM8S105C6</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -48035,14 +48035,14 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM8S207K8</t>
+          <t>STM8S105K4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -48057,14 +48057,14 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM8S207M8</t>
+          <t>STM8S105K6</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -48079,14 +48079,14 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM8S207MB</t>
+          <t>STM8S105S4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -48101,14 +48101,14 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM8S207R6</t>
+          <t>STM8S105S6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -48123,14 +48123,14 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM8S207R8</t>
+          <t>STM8S207C6</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -48152,7 +48152,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM8S207RB</t>
+          <t>STM8S207C8</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -48174,7 +48174,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM8S207S6</t>
+          <t>STM8S207CB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -48196,7 +48196,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM8S207S8</t>
+          <t>STM8S207K6</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -48218,7 +48218,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM8S207SB</t>
+          <t>STM8S207K8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -48240,7 +48240,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM8S208C6</t>
+          <t>STM8S207M8</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -48262,7 +48262,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM8S208C8</t>
+          <t>STM8S207MB</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -48284,7 +48284,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM8S208CB</t>
+          <t>STM8S207R6</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -48306,7 +48306,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM8S208MB</t>
+          <t>STM8S207R8</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -48328,7 +48328,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM8S208R8</t>
+          <t>STM8S207RB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -48350,7 +48350,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM8S208RB</t>
+          <t>STM8S207S6</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -48372,7 +48372,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM8S208S6</t>
+          <t>STM8S207S8</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -48394,7 +48394,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM8S903F3</t>
+          <t>STM8S207SB</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -48409,14 +48409,14 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Table 23. Total current consumption with code execution in run mode at V = 5 V; Table 32. Total current consumption and timing in forced reset state; Table 33. Peripheral current consumption</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM8S903K3</t>
+          <t>STM8S208C6</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -48431,14 +48431,14 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Table 23. Total current consumption with code execution in run mode at V = 5 V; Table 32. Total current consumption and timing in forced reset state; Table 33. Peripheral current consumption</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM8SPLNB1</t>
+          <t>STM8S208C8</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -48453,14 +48453,14 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Table 24. Total current consumption at V = 5 V</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM8AF628A</t>
+          <t>STM8S208CB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -48475,14 +48475,14 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Table 29. Total current consumption with code execution in run mode at V = 5 V; Table 38. Total current consumption and timing in forced reset state; Table 39. Peripheral current consumption</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM8AF62AA</t>
+          <t>STM8S208MB</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -48497,14 +48497,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 29. Total current consumption with code execution in run mode at V = 5 V; Table 38. Total current consumption and timing in forced reset state; Table 39. Peripheral current consumption</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM8AL3188</t>
+          <t>STM8S208R8</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -48519,14 +48519,14 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM8AL3189</t>
+          <t>STM8S208RB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -48541,19 +48541,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM8AL318A</t>
+          <t>STM8S208S6</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -48563,14 +48563,14 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM8AL318A</t>
+          <t>STM8S903F3</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -48585,14 +48585,14 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 23. Total current consumption with code execution in run mode at V = 5 V; Table 32. Total current consumption and timing in forced reset state; Table 33. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM8AL31E88</t>
+          <t>STM8S903K3</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -48607,19 +48607,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 23. Total current consumption with code execution in run mode at V = 5 V; Table 32. Total current consumption and timing in forced reset state; Table 33. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM8AL31E89</t>
+          <t>STM8SPLNB1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -48629,14 +48629,14 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. Total current consumption at V = 5 V</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM8AL31E89</t>
+          <t>STM8AF628A</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48651,19 +48651,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 29. Total current consumption with code execution in run mode at V = 5 V; Table 38. Total current consumption and timing in forced reset state; Table 39. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM8AL31E8A</t>
+          <t>STM8AF62AA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -48673,14 +48673,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 29. Total current consumption with code execution in run mode at V = 5 V; Table 38. Total current consumption and timing in forced reset state; Table 39. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM8AL31E8A</t>
+          <t>STM8AL3188</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -48702,7 +48702,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM8TL52F4</t>
+          <t>STM8AL3189</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -48717,19 +48717,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
+          <t>Table 29. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM8TL52F4</t>
+          <t>STM8AL318A</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -48739,14 +48739,14 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM8TL52G4</t>
+          <t>STM8AL318A</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -48761,27 +48761,467 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
+          <t>Table 29. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>STM8AL31E88</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>STM8AL31E89</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>STM8AL31E89</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>STM8AL31E8A</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>STM8AL31E8A</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>STM8AL3L88</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>STM8AL3L89</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>STM8AL3L8A</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>STM8AL3LE88</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>STM8AL3LE89</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>STM8AL3LE8A</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>STM8TL52F4</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>STM8TL52F4</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
           <t>STM8TL52G4</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>STM8TL52G4</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
         <is>
           <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>STM8TL53C4</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>STM8TL53C4</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>STM8TL53F4</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>STM8TL53F4</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>STM8TL53G4</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>STM8TL53G4</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
         <is>
           <t>Table 19. Total current consumption in Run mode (1)</t>
         </is>

--- a/product_selector_out/STM8 8-bit MCUs.xlsx
+++ b/product_selector_out/STM8 8-bit MCUs.xlsx
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AG43" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="AG44" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="AG45" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="AG46" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -21591,7 +21591,7 @@
       </c>
       <c r="AG135" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="AG136" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="AG137" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AG138" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="AG139" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22426,7 +22426,7 @@
       </c>
       <c r="AG140" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22927,7 +22927,7 @@
       </c>
       <c r="AG143" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -23094,7 +23094,7 @@
       </c>
       <c r="AG144" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -23261,7 +23261,7 @@
       </c>
       <c r="AG145" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -29099,19 +29099,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="X43" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z43" s="6" t="inlineStr">
@@ -29149,9 +29149,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG43" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -29266,19 +29266,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="X44" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z44" s="6" t="inlineStr">
@@ -29316,9 +29316,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG44" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -29433,19 +29433,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W45" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="X45" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y45" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z45" s="6" t="inlineStr">
@@ -29483,9 +29483,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG45" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -29600,19 +29600,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="X46" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y46" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z46" s="6" t="inlineStr">
@@ -29650,9 +29650,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG46" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44473,9 +44473,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y135" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y135" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z135" s="6" t="inlineStr">
@@ -44513,9 +44513,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG135" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG135" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44640,9 +44640,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y136" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y136" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z136" s="6" t="inlineStr">
@@ -44680,9 +44680,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG136" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG136" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44807,9 +44807,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y137" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y137" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z137" s="6" t="inlineStr">
@@ -44847,9 +44847,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG137" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG137" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44974,9 +44974,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y138" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y138" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z138" s="6" t="inlineStr">
@@ -45014,9 +45014,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG138" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG138" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -45141,9 +45141,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y139" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y139" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z139" s="6" t="inlineStr">
@@ -45181,9 +45181,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG139" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG139" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -45308,9 +45308,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y140" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y140" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z140" s="6" t="inlineStr">
@@ -45348,9 +45348,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG140" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG140" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -45799,24 +45799,24 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W143" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="X143" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y143" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="Z143" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W143" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X143" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y143" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Z143" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AA143" s="7" t="inlineStr">
@@ -45849,9 +45849,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG143" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG143" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -45966,24 +45966,24 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W144" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="X144" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y144" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="Z144" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W144" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X144" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y144" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Z144" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AA144" s="7" t="inlineStr">
@@ -46016,9 +46016,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG144" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG144" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -46133,24 +46133,24 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W145" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="X145" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y145" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="Z145" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W145" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X145" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y145" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Z145" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AA145" s="7" t="inlineStr">
@@ -46183,9 +46183,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG145" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG145" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -46204,7 +46204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -46678,12 +46678,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM8AL3L46</t>
+          <t>STM8L001J3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -46693,14 +46693,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM8AL3L46</t>
+          <t>STM8L050J3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -46715,19 +46715,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 25. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM8AL3L48</t>
+          <t>STM8L051F3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -46737,14 +46737,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM8AL3L48</t>
+          <t>STM8L052R8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -46759,19 +46759,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 17. Total current consumption in Run mode; Table 25. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM8AL3L66</t>
+          <t>STM8L052R8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -46781,14 +46781,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 17. Total current consumption in Run mode</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM8AL3L66</t>
+          <t>STM8L101F1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -46803,19 +46803,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM8AL3L68</t>
+          <t>STM8L101F2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -46825,14 +46825,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM8AL3L68</t>
+          <t>STM8L101F3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -46847,14 +46847,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM8L001J3</t>
+          <t>STM8L101G2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -46869,14 +46869,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 19. Peripheral current consumption</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM8L050J3</t>
+          <t>STM8L101G3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -46891,14 +46891,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption under external reset</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM8L051F3</t>
+          <t>STM8L101K3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -46913,14 +46913,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption under external reset</t>
+          <t>Table 21. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM8L052R8</t>
+          <t>STM8L151C2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -46935,19 +46935,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 17. Total current consumption in Run mode; Table 25. Current consumption under external reset</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM8L052R8</t>
+          <t>STM8L151C3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -46957,14 +46957,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 17. Total current consumption in Run mode</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM8L101F1</t>
+          <t>STM8L151C4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -46979,14 +46979,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 28. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM8L101F2</t>
+          <t>STM8L151C6</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -47001,14 +47001,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM8L101F3</t>
+          <t>STM8L151C8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -47023,14 +47023,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM8L101G2</t>
+          <t>STM8L151F2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -47045,14 +47045,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM8L101G3</t>
+          <t>STM8L151F3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -47067,14 +47067,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM8L101K3</t>
+          <t>STM8L151G2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -47089,14 +47089,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 21. Peripheral current consumption</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM8L151C2</t>
+          <t>STM8L151G3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -47118,7 +47118,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM8L151C3</t>
+          <t>STM8L151G4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -47140,7 +47140,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM8L151C4</t>
+          <t>STM8L151G6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -47155,14 +47155,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 28. Current consumption under external reset</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM8L151C6</t>
+          <t>STM8L151K2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -47184,7 +47184,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM8L151C8</t>
+          <t>STM8L151K3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -47206,7 +47206,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM8L151F2</t>
+          <t>STM8L151K4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -47228,7 +47228,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM8L151F3</t>
+          <t>STM8L151K6</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -47250,7 +47250,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM8L151G2</t>
+          <t>STM8L151M8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -47272,7 +47272,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM8L151G3</t>
+          <t>STM8L151R6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -47287,19 +47287,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 20. Total current consumption in Run mode; Table 28. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM8L151G4</t>
+          <t>STM8L151R6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -47309,14 +47309,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 20. Total current consumption in Run mode</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM8L151G6</t>
+          <t>STM8L151R8</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -47338,7 +47338,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM8L151K2</t>
+          <t>STM8L152C4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -47360,7 +47360,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM8L151K3</t>
+          <t>STM8L152C6</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -47382,7 +47382,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM8L151K4</t>
+          <t>STM8L152C8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -47404,7 +47404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM8L151K6</t>
+          <t>STM8L152K4</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -47426,7 +47426,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM8L151M8</t>
+          <t>STM8L152K6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -47448,7 +47448,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM8L151R6</t>
+          <t>STM8L152K8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -47463,19 +47463,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption in Run mode; Table 28. Current consumption under external reset</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM8L151R6</t>
+          <t>STM8L152M8</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -47485,14 +47485,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption in Run mode</t>
+          <t>Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM8L151R8</t>
+          <t>STM8L152R6</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -47514,7 +47514,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM8L152C4</t>
+          <t>STM8L152R8</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -47536,7 +47536,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM8L152C6</t>
+          <t>STM8L162M8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -47551,19 +47551,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 19. Total current consumption in Run mode; Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM8L152C8</t>
+          <t>STM8L162M8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -47573,14 +47573,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 19. Total current consumption in Run mode</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM8L152K4</t>
+          <t>STM8L162R8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -47595,19 +47595,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 19. Total current consumption in Run mode; Table 27. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM8L152K6</t>
+          <t>STM8L162R8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -47617,14 +47617,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 19. Total current consumption in Run mode</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM8L152K8</t>
+          <t>STM8S001J3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -47639,14 +47639,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM8L152M8</t>
+          <t>STM8S003F3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -47661,14 +47661,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 30. Total current consumption and timing in forced reset state; Table 31. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM8L152R6</t>
+          <t>STM8S003K3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -47683,14 +47683,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM8L152R8</t>
+          <t>STM8S005C6</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -47705,14 +47705,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption under external reset</t>
+          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM8L162M8</t>
+          <t>STM8S005K6</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -47727,19 +47727,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 19. Total current consumption in Run mode; Table 27. Current consumption under external reset</t>
+          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM8L162M8</t>
+          <t>STM8S007C8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -47749,14 +47749,14 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 19. Total current consumption in Run mode</t>
+          <t>Table 27. Total current consumption and timing in forced reset state; Table 28. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM8L162R8</t>
+          <t>STM8S103F2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -47771,19 +47771,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 19. Total current consumption in Run mode; Table 27. Current consumption under external reset</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM8L162R8</t>
+          <t>STM8S103F3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -47793,14 +47793,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 19. Total current consumption in Run mode</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM8S001J3</t>
+          <t>STM8S103K3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -47815,14 +47815,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM8S003F3</t>
+          <t>STM8S105C4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -47837,14 +47837,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 30. Total current consumption and timing in forced reset state; Table 31. Peripheral current consumption</t>
+          <t>Table 29. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM8S003K3</t>
+          <t>STM8S105C6</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -47859,14 +47859,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM8S005C6</t>
+          <t>STM8S105K4</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -47881,14 +47881,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM8S005K6</t>
+          <t>STM8S105K6</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -47903,14 +47903,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 28. Total current consumption and timing in forced reset state; Table 29. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM8S007C8</t>
+          <t>STM8S105S4</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -47925,14 +47925,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 27. Total current consumption and timing in forced reset state; Table 28. Peripheral current consumption</t>
+          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM8S103F2</t>
+          <t>STM8S105S6</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -47954,7 +47954,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM8S103F3</t>
+          <t>STM8S207C6</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -47969,14 +47969,14 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM8S103K3</t>
+          <t>STM8S207C8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -47991,14 +47991,14 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM8S105C4</t>
+          <t>STM8S207CB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -48013,14 +48013,14 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 29. Total current consumption and timing in forced reset state</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM8S105C6</t>
+          <t>STM8S207K6</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -48035,14 +48035,14 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM8S105K4</t>
+          <t>STM8S207K8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -48057,14 +48057,14 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM8S105K6</t>
+          <t>STM8S207M8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -48079,14 +48079,14 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM8S105S4</t>
+          <t>STM8S207MB</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -48101,14 +48101,14 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM8S105S6</t>
+          <t>STM8S207R6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -48123,14 +48123,14 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 21. Total current consumption with code execution in run mode at V = 5 V; Table 30. Total current consumption and timing in forced reset state</t>
+          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM8S207C6</t>
+          <t>STM8S207R8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -48152,7 +48152,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM8S207C8</t>
+          <t>STM8S207RB</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -48174,7 +48174,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM8S207CB</t>
+          <t>STM8S207S6</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -48196,7 +48196,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM8S207K6</t>
+          <t>STM8S207S8</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -48218,7 +48218,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM8S207K8</t>
+          <t>STM8S207SB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -48240,7 +48240,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM8S207M8</t>
+          <t>STM8S208C6</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -48262,7 +48262,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM8S207MB</t>
+          <t>STM8S208C8</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -48284,7 +48284,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM8S207R6</t>
+          <t>STM8S208CB</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -48306,7 +48306,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM8S207R8</t>
+          <t>STM8S208MB</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -48328,7 +48328,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM8S207RB</t>
+          <t>STM8S208R8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -48350,7 +48350,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM8S207S6</t>
+          <t>STM8S208RB</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -48372,7 +48372,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM8S207S8</t>
+          <t>STM8S208S6</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -48394,7 +48394,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM8S207SB</t>
+          <t>STM8S903F3</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -48409,14 +48409,14 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 23. Total current consumption with code execution in run mode at V = 5 V; Table 32. Total current consumption and timing in forced reset state; Table 33. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM8S208C6</t>
+          <t>STM8S903K3</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -48431,14 +48431,14 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 23. Total current consumption with code execution in run mode at V = 5 V; Table 32. Total current consumption and timing in forced reset state; Table 33. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM8S208C8</t>
+          <t>STM8SPLNB1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -48453,14 +48453,14 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 24. Total current consumption at V = 5 V</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM8S208CB</t>
+          <t>STM8AF628A</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -48475,14 +48475,14 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 29. Total current consumption with code execution in run mode at V = 5 V; Table 38. Total current consumption and timing in forced reset state; Table 39. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM8S208MB</t>
+          <t>STM8AF62AA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -48497,14 +48497,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 29. Total current consumption with code execution in run mode at V = 5 V; Table 38. Total current consumption and timing in forced reset state; Table 39. Peripheral current consumption</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM8S208R8</t>
+          <t>STM8AL3188</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -48519,14 +48519,14 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 29. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM8S208RB</t>
+          <t>STM8AL3189</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -48541,19 +48541,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 29. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM8S208S6</t>
+          <t>STM8AL318A</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -48563,14 +48563,14 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Table 20. Total current consumption with code execution in run mode at V = 5 V; Table 29. Total current consumption and timing in forced reset state; Table 30. Peripheral current consumption</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM8S903F3</t>
+          <t>STM8AL318A</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -48585,14 +48585,14 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 23. Total current consumption with code execution in run mode at V = 5 V; Table 32. Total current consumption and timing in forced reset state; Table 33. Peripheral current consumption</t>
+          <t>Table 29. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM8S903K3</t>
+          <t>STM8AL31E88</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -48607,19 +48607,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Table 23. Total current consumption with code execution in run mode at V = 5 V; Table 32. Total current consumption and timing in forced reset state; Table 33. Peripheral current consumption</t>
+          <t>Table 29. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM8SPLNB1</t>
+          <t>STM8AL31E89</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -48629,14 +48629,14 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 24. Total current consumption at V = 5 V</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM8AF628A</t>
+          <t>STM8AL31E89</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48651,19 +48651,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Table 29. Total current consumption with code execution in run mode at V = 5 V; Table 38. Total current consumption and timing in forced reset state; Table 39. Peripheral current consumption</t>
+          <t>Table 29. Current consumption under external reset</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM8AF62AA</t>
+          <t>STM8AL31E8A</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -48673,14 +48673,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 29. Total current consumption with code execution in run mode at V = 5 V; Table 38. Total current consumption and timing in forced reset state; Table 39. Peripheral current consumption</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM8AL3188</t>
+          <t>STM8AL31E8A</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -48702,7 +48702,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM8AL3189</t>
+          <t>STM8TL52F4</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -48717,19 +48717,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM8AL318A</t>
+          <t>STM8TL52F4</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -48739,14 +48739,14 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM8AL318A</t>
+          <t>STM8TL52G4</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -48761,19 +48761,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 29. Current consumption under external reset</t>
+          <t>Table 19. Total current consumption in Run mode (1)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM8AL31E88</t>
+          <t>STM8TL52G4</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -48782,446 +48782,6 @@
         </is>
       </c>
       <c r="D117" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>STM8AL31E89</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>STM8AL31E89</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>STM8AL31E8A</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>STM8AL31E8A</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>STM8AL3L88</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>STM8AL3L89</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>STM8AL3L8A</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>STM8AL3LE88</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>STM8AL3LE89</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>STM8AL3LE8A</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>STM8TL52F4</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>STM8TL52F4</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>STM8TL52G4</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>STM8TL52G4</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>STM8TL53C4</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>STM8TL53C4</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>STM8TL53F4</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>STM8TL53F4</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>STM8TL53G4</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Table 19. Total current consumption in Run mode (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>STM8TL53G4</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
         <is>
           <t>Table 19. Total current consumption in Run mode (1)</t>
         </is>

--- a/product_selector_out/STM8 8-bit MCUs.xlsx
+++ b/product_selector_out/STM8 8-bit MCUs.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG145"/>
+  <dimension ref="A1:AH145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.3671875" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,8 @@
     <col width="23.46484375" customWidth="1" min="30" max="30"/>
     <col width="11.6328125" customWidth="1" min="31" max="31"/>
     <col width="43.6484375" customWidth="1" min="32" max="32"/>
-    <col width="52" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="52" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -716,6 +717,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -883,6 +889,11 @@
       </c>
       <c r="AG11" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH11" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -1050,6 +1061,11 @@
       </c>
       <c r="AG12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -1217,6 +1233,11 @@
       </c>
       <c r="AG13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -1384,6 +1405,11 @@
       </c>
       <c r="AG14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -1551,6 +1577,11 @@
       </c>
       <c r="AG15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -1718,6 +1749,11 @@
       </c>
       <c r="AG16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -1885,6 +1921,11 @@
       </c>
       <c r="AG17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -2052,6 +2093,11 @@
       </c>
       <c r="AG18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -2219,6 +2265,11 @@
       </c>
       <c r="AG19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -2386,6 +2437,11 @@
       </c>
       <c r="AG20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -2553,6 +2609,11 @@
       </c>
       <c r="AG21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -2720,6 +2781,11 @@
       </c>
       <c r="AG22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -2887,6 +2953,11 @@
       </c>
       <c r="AG23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -3054,6 +3125,11 @@
       </c>
       <c r="AG24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6246.pdf</t>
         </is>
       </c>
@@ -3221,6 +3297,11 @@
       </c>
       <c r="AG25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6246.pdf</t>
         </is>
       </c>
@@ -3388,6 +3469,11 @@
       </c>
       <c r="AG26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6246.pdf</t>
         </is>
       </c>
@@ -3555,6 +3641,11 @@
       </c>
       <c r="AG27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6246.pdf</t>
         </is>
       </c>
@@ -3722,6 +3813,11 @@
       </c>
       <c r="AG28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -3889,6 +3985,11 @@
       </c>
       <c r="AG29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -4056,6 +4157,11 @@
       </c>
       <c r="AG30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -4223,6 +4329,11 @@
       </c>
       <c r="AG31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -4390,6 +4501,11 @@
       </c>
       <c r="AG32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -4557,6 +4673,11 @@
       </c>
       <c r="AG33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -4724,6 +4845,11 @@
       </c>
       <c r="AG34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -4891,6 +5017,11 @@
       </c>
       <c r="AG35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6366.pdf</t>
         </is>
       </c>
@@ -5058,6 +5189,11 @@
       </c>
       <c r="AG36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6388.pdf</t>
         </is>
       </c>
@@ -5225,6 +5361,11 @@
       </c>
       <c r="AG37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -5392,6 +5533,11 @@
       </c>
       <c r="AG38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -5559,6 +5705,11 @@
       </c>
       <c r="AG39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -5726,6 +5877,11 @@
       </c>
       <c r="AG40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -5893,6 +6049,11 @@
       </c>
       <c r="AG41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -6060,6 +6221,11 @@
       </c>
       <c r="AG42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -6230,6 +6396,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH43" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -6397,6 +6568,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH44" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -6564,6 +6740,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH45" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -6731,6 +6912,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH46" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -6895,6 +7081,11 @@
       </c>
       <c r="AG47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l001j3.pdf</t>
         </is>
       </c>
@@ -7062,6 +7253,11 @@
       </c>
       <c r="AG48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l050j3.pdf</t>
         </is>
       </c>
@@ -7229,6 +7425,11 @@
       </c>
       <c r="AG49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l051f3.pdf</t>
         </is>
       </c>
@@ -7396,6 +7597,11 @@
       </c>
       <c r="AG50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l052c6.pdf</t>
         </is>
       </c>
@@ -7563,6 +7769,11 @@
       </c>
       <c r="AG51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l052r8.pdf</t>
         </is>
       </c>
@@ -7730,6 +7941,11 @@
       </c>
       <c r="AG52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l101f1.pdf</t>
         </is>
       </c>
@@ -7897,6 +8113,11 @@
       </c>
       <c r="AG53" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l101f1.pdf</t>
         </is>
       </c>
@@ -8064,6 +8285,11 @@
       </c>
       <c r="AG54" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l101f1.pdf</t>
         </is>
       </c>
@@ -8231,6 +8457,11 @@
       </c>
       <c r="AG55" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l101f1.pdf</t>
         </is>
       </c>
@@ -8398,6 +8629,11 @@
       </c>
       <c r="AG56" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH56" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l101f1.pdf</t>
         </is>
       </c>
@@ -8565,6 +8801,11 @@
       </c>
       <c r="AG57" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l101f1.pdf</t>
         </is>
       </c>
@@ -8732,6 +8973,11 @@
       </c>
       <c r="AG58" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH58" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -8899,6 +9145,11 @@
       </c>
       <c r="AG59" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -9066,6 +9317,11 @@
       </c>
       <c r="AG60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c4.pdf</t>
         </is>
       </c>
@@ -9233,6 +9489,11 @@
       </c>
       <c r="AG61" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -9400,6 +9661,11 @@
       </c>
       <c r="AG62" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -9567,6 +9833,11 @@
       </c>
       <c r="AG63" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -9734,6 +10005,11 @@
       </c>
       <c r="AG64" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH64" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -9901,6 +10177,11 @@
       </c>
       <c r="AG65" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH65" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -10068,6 +10349,11 @@
       </c>
       <c r="AG66" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH66" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -10235,6 +10521,11 @@
       </c>
       <c r="AG67" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH67" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -10402,6 +10693,11 @@
       </c>
       <c r="AG68" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH68" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -10569,6 +10865,11 @@
       </c>
       <c r="AG69" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH69" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -10736,6 +11037,11 @@
       </c>
       <c r="AG70" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH70" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -10903,6 +11209,11 @@
       </c>
       <c r="AG71" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH71" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -11070,6 +11381,11 @@
       </c>
       <c r="AG72" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH72" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -11237,6 +11553,11 @@
       </c>
       <c r="AG73" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH73" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -11404,6 +11725,11 @@
       </c>
       <c r="AG74" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH74" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151r6.pdf</t>
         </is>
       </c>
@@ -11571,6 +11897,11 @@
       </c>
       <c r="AG75" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH75" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -11738,6 +12069,11 @@
       </c>
       <c r="AG76" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH76" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -11905,6 +12241,11 @@
       </c>
       <c r="AG77" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH77" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -12072,6 +12413,11 @@
       </c>
       <c r="AG78" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH78" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -12239,6 +12585,11 @@
       </c>
       <c r="AG79" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH79" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -12406,6 +12757,11 @@
       </c>
       <c r="AG80" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH80" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -12573,6 +12929,11 @@
       </c>
       <c r="AG81" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH81" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -12740,6 +13101,11 @@
       </c>
       <c r="AG82" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH82" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -12907,6 +13273,11 @@
       </c>
       <c r="AG83" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH83" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -13074,6 +13445,11 @@
       </c>
       <c r="AG84" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH84" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -13241,6 +13617,11 @@
       </c>
       <c r="AG85" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH85" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l162m8.pdf</t>
         </is>
       </c>
@@ -13408,6 +13789,11 @@
       </c>
       <c r="AG86" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH86" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l162m8.pdf</t>
         </is>
       </c>
@@ -13575,6 +13961,11 @@
       </c>
       <c r="AG87" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH87" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s001j3.pdf</t>
         </is>
       </c>
@@ -13742,6 +14133,11 @@
       </c>
       <c r="AG88" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH88" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s003f3.pdf</t>
         </is>
       </c>
@@ -13909,6 +14305,11 @@
       </c>
       <c r="AG89" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH89" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s001j3.pdf</t>
         </is>
       </c>
@@ -14076,6 +14477,11 @@
       </c>
       <c r="AG90" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH90" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s005c6.pdf</t>
         </is>
       </c>
@@ -14243,6 +14649,11 @@
       </c>
       <c r="AG91" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH91" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s001j3.pdf</t>
         </is>
       </c>
@@ -14410,6 +14821,11 @@
       </c>
       <c r="AG92" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH92" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s007c8.pdf</t>
         </is>
       </c>
@@ -14577,6 +14993,11 @@
       </c>
       <c r="AG93" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH93" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -14744,6 +15165,11 @@
       </c>
       <c r="AG94" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH94" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -14911,6 +15337,11 @@
       </c>
       <c r="AG95" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH95" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -15078,6 +15509,11 @@
       </c>
       <c r="AG96" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH96" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s105c4.pdf</t>
         </is>
       </c>
@@ -15245,6 +15681,11 @@
       </c>
       <c r="AG97" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH97" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -15412,6 +15853,11 @@
       </c>
       <c r="AG98" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH98" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -15579,6 +16025,11 @@
       </c>
       <c r="AG99" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH99" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -15746,6 +16197,11 @@
       </c>
       <c r="AG100" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH100" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -15913,6 +16369,11 @@
       </c>
       <c r="AG101" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH101" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -16080,6 +16541,11 @@
       </c>
       <c r="AG102" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH102" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -16247,6 +16713,11 @@
       </c>
       <c r="AG103" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH103" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -16414,6 +16885,11 @@
       </c>
       <c r="AG104" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH104" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -16581,6 +17057,11 @@
       </c>
       <c r="AG105" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH105" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -16748,6 +17229,11 @@
       </c>
       <c r="AG106" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH106" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -16915,6 +17401,11 @@
       </c>
       <c r="AG107" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH107" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -17082,6 +17573,11 @@
       </c>
       <c r="AG108" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH108" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -17249,6 +17745,11 @@
       </c>
       <c r="AG109" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH109" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -17416,6 +17917,11 @@
       </c>
       <c r="AG110" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH110" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -17583,6 +18089,11 @@
       </c>
       <c r="AG111" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH111" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -17750,6 +18261,11 @@
       </c>
       <c r="AG112" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH112" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -17917,6 +18433,11 @@
       </c>
       <c r="AG113" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH113" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -18084,6 +18605,11 @@
       </c>
       <c r="AG114" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH114" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -18251,6 +18777,11 @@
       </c>
       <c r="AG115" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH115" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -18418,6 +18949,11 @@
       </c>
       <c r="AG116" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH116" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -18585,6 +19121,11 @@
       </c>
       <c r="AG117" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH117" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -18752,6 +19293,11 @@
       </c>
       <c r="AG118" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH118" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -18919,6 +19465,11 @@
       </c>
       <c r="AG119" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH119" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -19086,6 +19637,11 @@
       </c>
       <c r="AG120" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH120" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -19253,6 +19809,11 @@
       </c>
       <c r="AG121" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH121" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -19420,6 +19981,11 @@
       </c>
       <c r="AG122" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH122" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s903k3.pdf</t>
         </is>
       </c>
@@ -19587,6 +20153,11 @@
       </c>
       <c r="AG123" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH123" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s903k3.pdf</t>
         </is>
       </c>
@@ -19754,6 +20325,11 @@
       </c>
       <c r="AG124" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH124" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8splnb1.pdf</t>
         </is>
       </c>
@@ -19921,6 +20497,11 @@
       </c>
       <c r="AG125" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH125" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -20088,6 +20669,11 @@
       </c>
       <c r="AG126" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH126" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af5268.pdf</t>
         </is>
       </c>
@@ -20255,6 +20841,11 @@
       </c>
       <c r="AG127" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH127" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -20422,6 +21013,11 @@
       </c>
       <c r="AG128" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH128" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6213.pdf</t>
         </is>
       </c>
@@ -20589,6 +21185,11 @@
       </c>
       <c r="AG129" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH129" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
         </is>
       </c>
@@ -20756,6 +21357,11 @@
       </c>
       <c r="AG130" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH130" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
         </is>
       </c>
@@ -20923,6 +21529,11 @@
       </c>
       <c r="AG131" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH131" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -21090,6 +21701,11 @@
       </c>
       <c r="AG132" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH132" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
         </is>
       </c>
@@ -21257,6 +21873,11 @@
       </c>
       <c r="AG133" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH133" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -21424,6 +22045,11 @@
       </c>
       <c r="AG134" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH134" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -21594,6 +22220,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH135" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -21761,6 +22392,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH136" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -21928,6 +22564,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH137" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -22095,6 +22736,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH138" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -22262,6 +22908,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH139" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
@@ -22429,6 +23080,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH140" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -22593,6 +23249,11 @@
       </c>
       <c r="AG141" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH141" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
         </is>
       </c>
@@ -22760,6 +23421,11 @@
       </c>
       <c r="AG142" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH142" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8tl52f4.pdf</t>
         </is>
       </c>
@@ -22930,6 +23596,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH143" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -23097,6 +23768,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH144" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -23264,11 +23940,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH145" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId1"/>
@@ -23418,7 +24099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG145"/>
+  <dimension ref="A1:AH145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -23454,6 +24135,7 @@
     <col width="16" customWidth="1" min="31" max="31"/>
     <col width="16" customWidth="1" min="32" max="32"/>
     <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23640,6 +24322,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -23805,7 +24492,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG11" s="6" t="inlineStr">
+      <c r="AG11" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH11" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23972,7 +24664,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG12" s="6" t="inlineStr">
+      <c r="AG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24139,7 +24836,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG13" s="6" t="inlineStr">
+      <c r="AG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24306,7 +25008,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG14" s="6" t="inlineStr">
+      <c r="AG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24473,7 +25180,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG15" s="6" t="inlineStr">
+      <c r="AG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24640,7 +25352,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG16" s="6" t="inlineStr">
+      <c r="AG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24807,7 +25524,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG17" s="6" t="inlineStr">
+      <c r="AG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24974,7 +25696,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG18" s="6" t="inlineStr">
+      <c r="AG18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25141,7 +25868,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG19" s="6" t="inlineStr">
+      <c r="AG19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25308,7 +26040,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG20" s="6" t="inlineStr">
+      <c r="AG20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25475,7 +26212,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG21" s="6" t="inlineStr">
+      <c r="AG21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25642,7 +26384,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG22" s="6" t="inlineStr">
+      <c r="AG22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25809,7 +26556,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG23" s="6" t="inlineStr">
+      <c r="AG23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25976,7 +26728,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG24" s="6" t="inlineStr">
+      <c r="AG24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26143,7 +26900,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG25" s="6" t="inlineStr">
+      <c r="AG25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26310,7 +27072,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG26" s="6" t="inlineStr">
+      <c r="AG26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26477,7 +27244,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG27" s="6" t="inlineStr">
+      <c r="AG27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26644,7 +27416,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG28" s="6" t="inlineStr">
+      <c r="AG28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26811,7 +27588,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG29" s="6" t="inlineStr">
+      <c r="AG29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26978,7 +27760,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG30" s="6" t="inlineStr">
+      <c r="AG30" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27145,7 +27932,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG31" s="6" t="inlineStr">
+      <c r="AG31" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27312,7 +28104,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG32" s="6" t="inlineStr">
+      <c r="AG32" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27479,7 +28276,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG33" s="6" t="inlineStr">
+      <c r="AG33" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27646,7 +28448,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG34" s="6" t="inlineStr">
+      <c r="AG34" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27813,7 +28620,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG35" s="6" t="inlineStr">
+      <c r="AG35" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27980,7 +28792,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG36" s="6" t="inlineStr">
+      <c r="AG36" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28147,7 +28964,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG37" s="6" t="inlineStr">
+      <c r="AG37" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28314,7 +29136,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG38" s="6" t="inlineStr">
+      <c r="AG38" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28481,7 +29308,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG39" s="6" t="inlineStr">
+      <c r="AG39" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28648,7 +29480,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG40" s="6" t="inlineStr">
+      <c r="AG40" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28815,7 +29652,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG41" s="6" t="inlineStr">
+      <c r="AG41" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28982,7 +29824,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG42" s="6" t="inlineStr">
+      <c r="AG42" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29154,6 +30001,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH43" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -29321,6 +30173,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH44" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -29488,6 +30345,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH45" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -29655,6 +30517,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH46" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -29817,7 +30684,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG47" s="6" t="inlineStr">
+      <c r="AG47" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29984,7 +30856,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG48" s="6" t="inlineStr">
+      <c r="AG48" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30151,7 +31028,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG49" s="6" t="inlineStr">
+      <c r="AG49" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30318,7 +31200,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG50" s="6" t="inlineStr">
+      <c r="AG50" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30485,7 +31372,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG51" s="6" t="inlineStr">
+      <c r="AG51" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30652,7 +31544,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG52" s="6" t="inlineStr">
+      <c r="AG52" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30819,7 +31716,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG53" s="6" t="inlineStr">
+      <c r="AG53" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30986,7 +31888,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG54" s="6" t="inlineStr">
+      <c r="AG54" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31153,7 +32060,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG55" s="6" t="inlineStr">
+      <c r="AG55" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31320,7 +32232,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG56" s="6" t="inlineStr">
+      <c r="AG56" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH56" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31487,7 +32404,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG57" s="6" t="inlineStr">
+      <c r="AG57" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31654,7 +32576,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG58" s="6" t="inlineStr">
+      <c r="AG58" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH58" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31821,7 +32748,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG59" s="6" t="inlineStr">
+      <c r="AG59" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31988,7 +32920,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG60" s="6" t="inlineStr">
+      <c r="AG60" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32155,7 +33092,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG61" s="6" t="inlineStr">
+      <c r="AG61" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32322,7 +33264,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG62" s="6" t="inlineStr">
+      <c r="AG62" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32489,7 +33436,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG63" s="6" t="inlineStr">
+      <c r="AG63" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32656,7 +33608,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG64" s="6" t="inlineStr">
+      <c r="AG64" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH64" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32823,7 +33780,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG65" s="6" t="inlineStr">
+      <c r="AG65" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH65" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32990,7 +33952,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG66" s="6" t="inlineStr">
+      <c r="AG66" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH66" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33157,7 +34124,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG67" s="6" t="inlineStr">
+      <c r="AG67" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH67" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33324,7 +34296,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG68" s="6" t="inlineStr">
+      <c r="AG68" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH68" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33491,7 +34468,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG69" s="6" t="inlineStr">
+      <c r="AG69" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH69" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33658,7 +34640,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG70" s="6" t="inlineStr">
+      <c r="AG70" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH70" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33825,7 +34812,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG71" s="6" t="inlineStr">
+      <c r="AG71" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH71" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33992,7 +34984,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG72" s="6" t="inlineStr">
+      <c r="AG72" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH72" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34159,7 +35156,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG73" s="6" t="inlineStr">
+      <c r="AG73" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH73" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34326,7 +35328,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG74" s="6" t="inlineStr">
+      <c r="AG74" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH74" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34493,7 +35500,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG75" s="6" t="inlineStr">
+      <c r="AG75" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH75" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34660,7 +35672,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG76" s="6" t="inlineStr">
+      <c r="AG76" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH76" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34827,7 +35844,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG77" s="6" t="inlineStr">
+      <c r="AG77" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH77" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34994,7 +36016,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG78" s="6" t="inlineStr">
+      <c r="AG78" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH78" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35161,7 +36188,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG79" s="6" t="inlineStr">
+      <c r="AG79" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH79" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35328,7 +36360,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG80" s="6" t="inlineStr">
+      <c r="AG80" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH80" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35495,7 +36532,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG81" s="6" t="inlineStr">
+      <c r="AG81" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH81" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35662,7 +36704,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG82" s="6" t="inlineStr">
+      <c r="AG82" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH82" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35829,7 +36876,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG83" s="6" t="inlineStr">
+      <c r="AG83" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH83" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35996,7 +37048,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG84" s="6" t="inlineStr">
+      <c r="AG84" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH84" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36163,7 +37220,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG85" s="6" t="inlineStr">
+      <c r="AG85" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH85" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36330,7 +37392,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG86" s="6" t="inlineStr">
+      <c r="AG86" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH86" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36497,7 +37564,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG87" s="6" t="inlineStr">
+      <c r="AG87" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH87" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36664,7 +37736,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG88" s="6" t="inlineStr">
+      <c r="AG88" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH88" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36831,7 +37908,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG89" s="6" t="inlineStr">
+      <c r="AG89" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH89" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36998,7 +38080,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG90" s="6" t="inlineStr">
+      <c r="AG90" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH90" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37165,7 +38252,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG91" s="6" t="inlineStr">
+      <c r="AG91" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH91" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37332,7 +38424,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG92" s="6" t="inlineStr">
+      <c r="AG92" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH92" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37499,7 +38596,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG93" s="6" t="inlineStr">
+      <c r="AG93" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH93" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37666,7 +38768,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG94" s="6" t="inlineStr">
+      <c r="AG94" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH94" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37833,7 +38940,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG95" s="6" t="inlineStr">
+      <c r="AG95" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH95" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38000,7 +39112,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG96" s="6" t="inlineStr">
+      <c r="AG96" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH96" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38167,7 +39284,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG97" s="6" t="inlineStr">
+      <c r="AG97" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH97" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38334,7 +39456,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG98" s="6" t="inlineStr">
+      <c r="AG98" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH98" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38501,7 +39628,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG99" s="6" t="inlineStr">
+      <c r="AG99" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH99" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38668,7 +39800,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG100" s="6" t="inlineStr">
+      <c r="AG100" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH100" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38835,7 +39972,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG101" s="6" t="inlineStr">
+      <c r="AG101" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH101" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39002,7 +40144,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG102" s="6" t="inlineStr">
+      <c r="AG102" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH102" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39169,7 +40316,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG103" s="6" t="inlineStr">
+      <c r="AG103" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH103" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39336,7 +40488,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG104" s="6" t="inlineStr">
+      <c r="AG104" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH104" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39503,7 +40660,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG105" s="6" t="inlineStr">
+      <c r="AG105" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH105" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39670,7 +40832,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG106" s="6" t="inlineStr">
+      <c r="AG106" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH106" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39837,7 +41004,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG107" s="6" t="inlineStr">
+      <c r="AG107" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH107" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40004,7 +41176,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG108" s="6" t="inlineStr">
+      <c r="AG108" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH108" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40171,7 +41348,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG109" s="6" t="inlineStr">
+      <c r="AG109" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH109" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40338,7 +41520,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG110" s="6" t="inlineStr">
+      <c r="AG110" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH110" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40505,7 +41692,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG111" s="6" t="inlineStr">
+      <c r="AG111" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH111" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40672,7 +41864,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG112" s="6" t="inlineStr">
+      <c r="AG112" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH112" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40839,7 +42036,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG113" s="6" t="inlineStr">
+      <c r="AG113" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH113" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41006,7 +42208,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG114" s="6" t="inlineStr">
+      <c r="AG114" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH114" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41173,7 +42380,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG115" s="6" t="inlineStr">
+      <c r="AG115" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH115" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41340,7 +42552,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG116" s="6" t="inlineStr">
+      <c r="AG116" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH116" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41507,7 +42724,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG117" s="6" t="inlineStr">
+      <c r="AG117" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH117" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41674,7 +42896,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG118" s="6" t="inlineStr">
+      <c r="AG118" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH118" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41841,7 +43068,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG119" s="6" t="inlineStr">
+      <c r="AG119" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH119" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42008,7 +43240,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG120" s="6" t="inlineStr">
+      <c r="AG120" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH120" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42175,7 +43412,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG121" s="6" t="inlineStr">
+      <c r="AG121" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH121" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42342,7 +43584,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG122" s="6" t="inlineStr">
+      <c r="AG122" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH122" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42509,7 +43756,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG123" s="6" t="inlineStr">
+      <c r="AG123" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH123" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42676,7 +43928,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG124" s="6" t="inlineStr">
+      <c r="AG124" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH124" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42843,7 +44100,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG125" s="6" t="inlineStr">
+      <c r="AG125" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH125" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43010,7 +44272,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG126" s="6" t="inlineStr">
+      <c r="AG126" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH126" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43177,7 +44444,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG127" s="6" t="inlineStr">
+      <c r="AG127" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH127" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43344,7 +44616,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG128" s="6" t="inlineStr">
+      <c r="AG128" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH128" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43511,7 +44788,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG129" s="6" t="inlineStr">
+      <c r="AG129" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH129" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43678,7 +44960,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG130" s="6" t="inlineStr">
+      <c r="AG130" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH130" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43845,7 +45132,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG131" s="6" t="inlineStr">
+      <c r="AG131" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH131" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44012,7 +45304,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG132" s="6" t="inlineStr">
+      <c r="AG132" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH132" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44179,7 +45476,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG133" s="6" t="inlineStr">
+      <c r="AG133" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH133" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44346,7 +45648,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG134" s="6" t="inlineStr">
+      <c r="AG134" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH134" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44518,6 +45825,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH135" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
@@ -44685,6 +45997,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH136" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
@@ -44852,6 +46169,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH137" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
@@ -45019,6 +46341,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH138" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
@@ -45186,6 +46513,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH139" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
@@ -45353,6 +46685,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH140" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
@@ -45515,7 +46852,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG141" s="6" t="inlineStr">
+      <c r="AG141" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH141" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45682,7 +47024,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG142" s="6" t="inlineStr">
+      <c r="AG142" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH142" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45854,6 +47201,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH143" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
@@ -46021,6 +47373,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH144" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
@@ -46188,11 +47545,16 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH145" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
